--- a/facility_management_forms/041_plant_maintenance_request_form--facility_management_forms.xlsx
+++ b/facility_management_forms/041_plant_maintenance_request_form--facility_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'repair'}</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Repair'}</t>
+          <t>Repair</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'scheduling'}</t>
+          <t>scheduling</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'Scheduling'}</t>
+          <t>Scheduling</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_50,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 50, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_60,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 60, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_200,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 200, 'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_210,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 210, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_220,_'name':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 220, 'name': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
